--- a/KURIKULUM2026_REVISI/027_RENCANA_RESTRUKTURISASI_KODE_MK_CORE_STI_KONTINU.xlsx
+++ b/KURIKULUM2026_REVISI/027_RENCANA_RESTRUKTURISASI_KODE_MK_CORE_STI_KONTINU.xlsx
@@ -1544,7 +1544,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>**`STI-624`**</t>
+          <t>**`STI-726`**</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>**`STI-625`**</t>
+          <t>**`STI-727`**</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>**`STI-626`**</t>
+          <t>**`STI-726`**</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>**`STI-627`**</t>
+          <t>**`STI-727`**</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>**`STI-627`**, `MKU-204`</t>
+          <t>**`STI-727`**, `MKU-204`</t>
         </is>
       </c>
     </row>
